--- a/DP/LP_Policy_Evaluation.xlsx
+++ b/DP/LP_Policy_Evaluation.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mhahsler\github\Introduction_to_Reinforcement_Learning\DP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6916408F-37D9-43A6-A569-BF5634D66DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC61C98-A4B7-4B4E-AA5A-19AB4F2E97F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LP Policy Evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$26:$F$27</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$22:$F$23</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$26</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$27</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$27</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$22</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$23</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'LP Policy Evaluation'!$F$23</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -39,9 +39,9 @@
     <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'LP Policy Evaluation'!$H$26</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'LP Policy Evaluation'!$H$27</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'LP Policy Evaluation'!$H$27</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'LP Policy Evaluation'!$G$22</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'LP Policy Evaluation'!$G$23</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'LP Policy Evaluation'!$G$23</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>Two-State MDP Policy Evaluation via Linear Programming</t>
   </si>
@@ -79,12 +79,6 @@
     <t>Interactive setup solving V(s1) and V(s2) using Bellman Expectation Constraints</t>
   </si>
   <si>
-    <t>1. MDP Parameters (Editable)</t>
-  </si>
-  <si>
-    <t>3. Linear Programming Constraint Lines</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -136,9 +130,6 @@
     <t>Transition probability from S2 to S2</t>
   </si>
   <si>
-    <t>2. Exact Optimal Solution (Intersection Point)</t>
-  </si>
-  <si>
     <t>State</t>
   </si>
   <si>
@@ -157,16 +148,40 @@
     <t>Constraint V(s1)</t>
   </si>
   <si>
-    <t>constraint</t>
-  </si>
-  <si>
     <t>Using the Solver</t>
   </si>
   <si>
     <t>objective (min)</t>
   </si>
   <si>
-    <t>Feasible region it the top tight triangle between the two constraint lines.</t>
+    <t xml:space="preserve"> MDP Parameters (Editable)</t>
+  </si>
+  <si>
+    <t>Exact Optimal Solution (Intersection Point)</t>
+  </si>
+  <si>
+    <t>For Visualization</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>V(s1)+V(s2)</t>
+  </si>
+  <si>
+    <t>Subject to:</t>
+  </si>
+  <si>
+    <t>V(s1) &gt;=  R1 + γ(P11 V(s1) + P12 V(s2))</t>
+  </si>
+  <si>
+    <t>V(s2) &gt;=  R2 + γ(P21 V(s1) + P22 V(s2))</t>
+  </si>
+  <si>
+    <t>Constraint Value</t>
   </si>
 </sst>
 </file>
@@ -224,7 +239,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,6 +250,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F497D"/>
         <bgColor rgb="FF1F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -265,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -274,18 +295,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,7 +410,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'LP Policy Evaluation'!$F$6</c:f>
+              <c:f>'LP Policy Evaluation'!$B$50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -411,7 +433,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$E$7:$E$22</c:f>
+              <c:f>'LP Policy Evaluation'!$A$51:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="16"/>
@@ -468,7 +490,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$F$7:$F$22</c:f>
+              <c:f>'LP Policy Evaluation'!$B$51:$B$66</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
@@ -535,7 +557,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'LP Policy Evaluation'!$G$6</c:f>
+              <c:f>'LP Policy Evaluation'!$C$50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -558,7 +580,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$E$7:$E$22</c:f>
+              <c:f>'LP Policy Evaluation'!$A$51:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="16"/>
@@ -615,7 +637,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$G$7:$G$22</c:f>
+              <c:f>'LP Policy Evaluation'!$C$51:$C$66</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
@@ -1543,15 +1565,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>244475</xdr:colOff>
+      <xdr:colOff>758825</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1435100</xdr:colOff>
+      <xdr:colOff>1949450</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1579,15 +1601,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1014009</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>159885</xdr:rowOff>
+      <xdr:colOff>950509</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>197985</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1611,7 +1633,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5930900" y="6089650"/>
+          <a:off x="5867400" y="5759450"/>
           <a:ext cx="4385859" cy="4217535"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1619,6 +1641,82 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2317750</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60C48705-7D16-9F62-6E3C-AD127D55B291}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="355600" y="8337550"/>
+          <a:ext cx="4387850" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Feasible region it the top tight triangle between the two constraint lines.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1909,11 +2007,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I29"/>
+  <dimension ref="A2:I66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.36328125" customWidth="1"/>
-    <col min="2" max="2" width="7.36328125" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" customWidth="1"/>
     <col min="3" max="3" width="36.54296875" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="19.90625" customWidth="1"/>
@@ -1933,400 +2031,450 @@
     </row>
     <row r="5" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12">
         <v>0.9</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="8">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9">
-        <f t="shared" ref="F7:F22" si="0">(E7*(1-$B$7*$B$10)-$B$8)/($B$7*$B$11)</f>
-        <v>10</v>
-      </c>
-      <c r="G7" s="9">
-        <f t="shared" ref="G7:G22" si="1">($B$9+$B$7*$B$12*E7)/(1-$B$7*$B$13)</f>
-        <v>15.263157894736848</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12"/>
+      <c r="C7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B9" s="13">
+        <v>2</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8">
+      <c r="H9" s="11"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="9">
+      <c r="B10" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="H14" s="11"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A17" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="H19" s="11"/>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8">
+        <f>(((1-$B$7*$B$13)*$B$8 + ($B$7*$B$11)*$B$9)/((1-$B$7*$B$10)*(1-$B$7*$B$13)-($B$7*$B$11)*($B$7*$B$12)))</f>
+        <v>17.031250000000004</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22">
+        <v>17.031249999999989</v>
+      </c>
+      <c r="G22">
+        <f>$B$8+$B$7*($B$10*F22+$B$11*F23)</f>
+        <v>17.031249999999989</v>
+      </c>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8">
+        <f>((($B$7*$B$12)*$B$8 + (1-$B$7*$B$10)*$B$9)/((1-$B$7*$B$10)*(1-$B$7*$B$13)-($B$7*$B$11)*($B$7*$B$12)))</f>
+        <v>18.593750000000011</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23">
+        <v>18.593749999999989</v>
+      </c>
+      <c r="G23">
+        <f>$B$9+$B$7*($B$12*F22+$B$13*F23)</f>
+        <v>18.593749999999989</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25">
+        <f>F22+F23</f>
+        <v>35.624999999999979</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A51" s="7">
+        <v>10</v>
+      </c>
+      <c r="B51" s="8">
+        <f t="shared" ref="B51:B66" si="0">(A51*(1-$B$7*$B$10)-$B$8)/($B$7*$B$11)</f>
+        <v>10</v>
+      </c>
+      <c r="C51" s="8">
+        <f t="shared" ref="C51:C66" si="1">($B$9+$B$7*$B$12*A51)/(1-$B$7*$B$13)</f>
+        <v>15.263157894736848</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A52" s="7">
+        <v>11</v>
+      </c>
+      <c r="B52" s="8">
         <f t="shared" si="0"/>
         <v>11.222222222222223</v>
       </c>
-      <c r="G8" s="9">
+      <c r="C52" s="8">
         <f t="shared" si="1"/>
         <v>15.736842105263163</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="10">
-        <v>2</v>
-      </c>
-      <c r="C9" s="7" t="s">
+    </row>
+    <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A53" s="7">
         <v>12</v>
       </c>
-      <c r="E9" s="8">
-        <v>12</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="B53" s="8">
         <f t="shared" si="0"/>
         <v>12.444444444444445</v>
       </c>
-      <c r="G9" s="9">
+      <c r="C53" s="8">
         <f t="shared" si="1"/>
         <v>16.21052631578948</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
+    </row>
+    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A54" s="7">
         <v>13</v>
       </c>
-      <c r="B10" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="8">
-        <v>13</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="B54" s="8">
         <f t="shared" si="0"/>
         <v>13.666666666666668</v>
       </c>
-      <c r="G10" s="9">
+      <c r="C54" s="8">
         <f t="shared" si="1"/>
         <v>16.684210526315795</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="12"/>
-    </row>
-    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="8">
+    </row>
+    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A55" s="7">
         <v>14</v>
       </c>
-      <c r="F11" s="9">
+      <c r="B55" s="8">
         <f t="shared" si="0"/>
         <v>14.888888888888891</v>
       </c>
-      <c r="G11" s="9">
+      <c r="C55" s="8">
         <f t="shared" si="1"/>
         <v>17.15789473684211</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="8">
+    </row>
+    <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A56" s="7">
         <v>15</v>
       </c>
-      <c r="F12" s="9">
+      <c r="B56" s="8">
         <f t="shared" si="0"/>
         <v>16.111111111111111</v>
       </c>
-      <c r="G12" s="9">
+      <c r="C56" s="8">
         <f t="shared" si="1"/>
         <v>17.631578947368425</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="8">
+    </row>
+    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A57" s="7">
         <v>16</v>
       </c>
-      <c r="F13" s="9">
+      <c r="B57" s="8">
         <f t="shared" si="0"/>
         <v>17.333333333333336</v>
       </c>
-      <c r="G13" s="9">
+      <c r="C57" s="8">
         <f t="shared" si="1"/>
         <v>18.105263157894743</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="E14" s="8">
+    </row>
+    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A58" s="7">
         <v>17</v>
       </c>
-      <c r="F14" s="9">
+      <c r="B58" s="8">
         <f t="shared" si="0"/>
         <v>18.555555555555557</v>
       </c>
-      <c r="G14" s="9">
+      <c r="C58" s="8">
         <f t="shared" si="1"/>
         <v>18.578947368421058</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="E15" s="8">
+    </row>
+    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A59" s="7">
         <v>18</v>
       </c>
-      <c r="F15" s="9">
+      <c r="B59" s="8">
         <f t="shared" si="0"/>
         <v>19.777777777777779</v>
       </c>
-      <c r="G15" s="9">
+      <c r="C59" s="8">
         <f t="shared" si="1"/>
         <v>19.052631578947373</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="8">
+    </row>
+    <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A60" s="7">
         <v>19</v>
       </c>
-      <c r="F16" s="9">
+      <c r="B60" s="8">
         <f t="shared" si="0"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="G16" s="9">
+      <c r="C60" s="8">
         <f t="shared" si="1"/>
         <v>19.526315789473689</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A17" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="8">
+    </row>
+    <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A61" s="7">
         <v>20</v>
       </c>
-      <c r="F17" s="9">
+      <c r="B61" s="8">
         <f t="shared" si="0"/>
         <v>22.222222222222221</v>
       </c>
-      <c r="G17" s="9">
+      <c r="C61" s="8">
         <f t="shared" si="1"/>
         <v>20.000000000000007</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="9">
-        <f>(((1-$B$7*$B$13)*$B$8 + ($B$7*$B$11)*$B$9)/((1-$B$7*$B$10)*(1-$B$7*$B$13)-($B$7*$B$11)*($B$7*$B$12)))</f>
-        <v>17.031250000000004</v>
-      </c>
-      <c r="E18" s="8">
+    </row>
+    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A62" s="7">
         <v>21</v>
       </c>
-      <c r="F18" s="9">
+      <c r="B62" s="8">
         <f t="shared" si="0"/>
         <v>23.444444444444446</v>
       </c>
-      <c r="G18" s="9">
+      <c r="C62" s="8">
         <f t="shared" si="1"/>
         <v>20.473684210526322</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="9">
-        <f>((($B$7*$B$12)*$B$8 + (1-$B$7*$B$10)*$B$9)/((1-$B$7*$B$10)*(1-$B$7*$B$13)-($B$7*$B$11)*($B$7*$B$12)))</f>
-        <v>18.593750000000011</v>
-      </c>
-      <c r="E19" s="8">
+    </row>
+    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A63" s="7">
         <v>22</v>
       </c>
-      <c r="F19" s="9">
+      <c r="B63" s="8">
         <f t="shared" si="0"/>
         <v>24.666666666666668</v>
       </c>
-      <c r="G19" s="9">
+      <c r="C63" s="8">
         <f t="shared" si="1"/>
         <v>20.947368421052641</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="E20" s="8">
+    </row>
+    <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A64" s="7">
         <v>23</v>
       </c>
-      <c r="F20" s="9">
+      <c r="B64" s="8">
         <f t="shared" si="0"/>
         <v>25.888888888888889</v>
       </c>
-      <c r="G20" s="9">
+      <c r="C64" s="8">
         <f t="shared" si="1"/>
         <v>21.421052631578956</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="E21" s="8">
+    </row>
+    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A65" s="7">
         <v>24</v>
       </c>
-      <c r="F21" s="9">
+      <c r="B65" s="8">
         <f t="shared" si="0"/>
         <v>27.111111111111114</v>
       </c>
-      <c r="G21" s="9">
+      <c r="C65" s="8">
         <f t="shared" si="1"/>
         <v>21.894736842105271</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="8">
+    </row>
+    <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.45">
+      <c r="A66" s="7">
         <v>25</v>
       </c>
-      <c r="F22" s="9">
+      <c r="B66" s="8">
         <f t="shared" si="0"/>
         <v>28.333333333333336</v>
       </c>
-      <c r="G22" s="9">
+      <c r="C66" s="8">
         <f t="shared" si="1"/>
         <v>22.368421052631586</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="E25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="E26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26">
-        <v>17.031249999999989</v>
-      </c>
-      <c r="H26">
-        <f>B8+B7*(B10*F26+B11*F27)</f>
-        <v>17.031249999999989</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="E27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27">
-        <v>18.593749999999989</v>
-      </c>
-      <c r="H27">
-        <f>B9+B7*(B12*F26+B13*F27)</f>
-        <v>18.593749999999989</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="E29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29">
-        <f>F26+F27</f>
-        <v>35.624999999999979</v>
       </c>
     </row>
   </sheetData>

--- a/DP/LP_Policy_Evaluation.xlsx
+++ b/DP/LP_Policy_Evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mhahsler\github\Introduction_to_Reinforcement_Learning\DP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC61C98-A4B7-4B4E-AA5A-19AB4F2E97F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA98FD2B-6735-4BA6-BC26-3244B8B0E67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>Two-State MDP Policy Evaluation via Linear Programming</t>
   </si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>Constraint Value</t>
+  </si>
+  <si>
+    <t>Objective</t>
   </si>
 </sst>
 </file>
@@ -259,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -282,6 +285,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -296,7 +310,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -307,7 +320,8 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,13 +374,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>LP</a:t>
+              <a:t>LP for 2-State MDP</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> for 2-State MDP</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -402,15 +411,15 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'LP Policy Evaluation'!$B$50</c:f>
+              <c:f>'LP Policy Evaluation'!$B$26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -420,7 +429,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -431,120 +440,36 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
+          <c:xVal>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$A$51:$A$66</c:f>
+              <c:f>'LP Policy Evaluation'!$A$27:$A$28</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>25</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$B$51:$B$66</c:f>
+              <c:f>'LP Policy Evaluation'!$B$27:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>-2.2222222222222223</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.222222222222223</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12.444444444444445</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13.666666666666668</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>14.888888888888891</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>16.111111111111111</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17.333333333333336</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.555555555555557</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>19.777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>21.000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22.222222222222221</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>23.444444444444446</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>24.666666666666668</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>25.888888888888889</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>27.111111111111114</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>28.333333333333336</c:v>
+                  <c:v>58.888888888888893</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -557,7 +482,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'LP Policy Evaluation'!$C$50</c:f>
+              <c:f>'LP Policy Evaluation'!$C$26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -567,7 +492,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -578,124 +503,96 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
+          <c:xVal>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$A$51:$A$66</c:f>
+              <c:f>'LP Policy Evaluation'!$A$27:$A$28</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>25</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
-              <c:f>'LP Policy Evaluation'!$C$51:$C$66</c:f>
+              <c:f>'LP Policy Evaluation'!$C$27:$C$28</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>15.263157894736848</c:v>
+                  <c:v>10.526315789473687</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.736842105263163</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16.21052631578948</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.684210526315795</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>17.15789473684211</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>17.631578947368425</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>18.105263157894743</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.578947368421058</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>19.052631578947373</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19.526315789473689</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.473684210526322</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.947368421052641</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>21.421052631578956</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>21.894736842105271</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>22.368421052631586</c:v>
+                  <c:v>34.210526315789487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-B228-4C8E-B00A-22D066A9B0B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Objective</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'LP Policy Evaluation'!$A$59:$A$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35.625000000000014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'LP Policy Evaluation'!$B$59:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0" formatCode="0.00">
+                  <c:v>35.625000000000014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5503-4FC9-A6DD-8C4A896B2C1D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -707,17 +604,31 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="938217840"/>
         <c:axId val="1015613472"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="938217840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="40"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -773,7 +684,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -782,8 +693,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -812,15 +723,14 @@
         </c:txPr>
         <c:crossAx val="1015613472"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1015613472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="40"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -899,8 +809,14 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -926,7 +842,7 @@
         </c:txPr>
         <c:crossAx val="938217840"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1045,7 +961,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1072,8 +988,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1153,11 +1069,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1168,11 +1079,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1184,7 +1090,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1204,9 +1110,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1219,10 +1122,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1262,22 +1165,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1382,8 +1286,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1515,19 +1419,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1541,6 +1446,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1565,15 +1481,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>758825</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1949450</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>1714500</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1608,8 +1524,8 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>950509</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>197985</xdr:rowOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>13835</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1646,15 +1562,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:colOff>527050</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2317750</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>2489200</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1669,8 +1585,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="355600" y="8337550"/>
-          <a:ext cx="4387850" cy="285750"/>
+          <a:off x="527050" y="10591800"/>
+          <a:ext cx="5359400" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2007,7 +1923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I66"/>
+  <dimension ref="A2:I60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.36328125" customWidth="1"/>
@@ -2049,134 +1965,134 @@
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>0.9</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>2</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>0.5</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <v>0.5</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>0.1</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9"/>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>0.9</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="H14" s="11"/>
-      <c r="I14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="9"/>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="9"/>
     </row>
     <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="H19" s="11"/>
-      <c r="I19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
@@ -2185,16 +2101,16 @@
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="10"/>
+      <c r="I20" s="9"/>
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.45">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="4" t="s">
@@ -2203,13 +2119,13 @@
       <c r="G21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="10"/>
+      <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <f>(((1-$B$7*$B$13)*$B$8 + ($B$7*$B$11)*$B$9)/((1-$B$7*$B$10)*(1-$B$7*$B$13)-($B$7*$B$11)*($B$7*$B$12)))</f>
         <v>17.031250000000004</v>
       </c>
@@ -2223,13 +2139,13 @@
         <f>$B$8+$B$7*($B$10*F22+$B$11*F23)</f>
         <v>17.031249999999989</v>
       </c>
-      <c r="I22" s="10"/>
+      <c r="I22" s="9"/>
     </row>
     <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <f>((($B$7*$B$12)*$B$8 + (1-$B$7*$B$10)*$B$9)/((1-$B$7*$B$10)*(1-$B$7*$B$13)-($B$7*$B$11)*($B$7*$B$12)))</f>
         <v>18.593750000000011</v>
       </c>
@@ -2245,6 +2161,9 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
       <c r="E25" t="s">
         <v>26</v>
       </c>
@@ -2253,228 +2172,67 @@
         <v>35.624999999999979</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A51" s="7">
-        <v>10</v>
-      </c>
-      <c r="B51" s="8">
-        <f t="shared" ref="B51:B66" si="0">(A51*(1-$B$7*$B$10)-$B$8)/($B$7*$B$11)</f>
-        <v>10</v>
-      </c>
-      <c r="C51" s="8">
-        <f t="shared" ref="C51:C66" si="1">($B$9+$B$7*$B$12*A51)/(1-$B$7*$B$13)</f>
-        <v>15.263157894736848</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A52" s="7">
-        <v>11</v>
-      </c>
-      <c r="B52" s="8">
-        <f t="shared" si="0"/>
-        <v>11.222222222222223</v>
-      </c>
-      <c r="C52" s="8">
-        <f t="shared" si="1"/>
-        <v>15.736842105263163</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A53" s="7">
-        <v>12</v>
-      </c>
-      <c r="B53" s="8">
-        <f t="shared" si="0"/>
-        <v>12.444444444444445</v>
-      </c>
-      <c r="C53" s="8">
-        <f t="shared" si="1"/>
-        <v>16.21052631578948</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A54" s="7">
-        <v>13</v>
-      </c>
-      <c r="B54" s="8">
-        <f t="shared" si="0"/>
-        <v>13.666666666666668</v>
-      </c>
-      <c r="C54" s="8">
-        <f t="shared" si="1"/>
-        <v>16.684210526315795</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A55" s="7">
-        <v>14</v>
-      </c>
-      <c r="B55" s="8">
-        <f t="shared" si="0"/>
-        <v>14.888888888888891</v>
-      </c>
-      <c r="C55" s="8">
-        <f t="shared" si="1"/>
-        <v>17.15789473684211</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A56" s="7">
-        <v>15</v>
-      </c>
-      <c r="B56" s="8">
-        <f t="shared" si="0"/>
-        <v>16.111111111111111</v>
-      </c>
-      <c r="C56" s="8">
-        <f t="shared" si="1"/>
-        <v>17.631578947368425</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A57" s="7">
-        <v>16</v>
-      </c>
-      <c r="B57" s="8">
-        <f t="shared" si="0"/>
-        <v>17.333333333333336</v>
-      </c>
-      <c r="C57" s="8">
-        <f t="shared" si="1"/>
-        <v>18.105263157894743</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A58" s="7">
-        <v>17</v>
-      </c>
-      <c r="B58" s="8">
-        <f t="shared" si="0"/>
-        <v>18.555555555555557</v>
-      </c>
-      <c r="C58" s="8">
-        <f t="shared" si="1"/>
-        <v>18.578947368421058</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A59" s="7">
-        <v>18</v>
-      </c>
-      <c r="B59" s="8">
-        <f t="shared" si="0"/>
-        <v>19.777777777777779</v>
-      </c>
-      <c r="C59" s="8">
-        <f t="shared" si="1"/>
-        <v>19.052631578947373</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A60" s="7">
-        <v>19</v>
-      </c>
-      <c r="B60" s="8">
-        <f t="shared" si="0"/>
-        <v>21.000000000000004</v>
-      </c>
-      <c r="C60" s="8">
-        <f t="shared" si="1"/>
-        <v>19.526315789473689</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A61" s="7">
-        <v>20</v>
-      </c>
-      <c r="B61" s="8">
-        <f t="shared" si="0"/>
-        <v>22.222222222222221</v>
-      </c>
-      <c r="C61" s="8">
-        <f t="shared" si="1"/>
-        <v>20.000000000000007</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A62" s="7">
-        <v>21</v>
-      </c>
-      <c r="B62" s="8">
-        <f t="shared" si="0"/>
-        <v>23.444444444444446</v>
-      </c>
-      <c r="C62" s="8">
-        <f t="shared" si="1"/>
-        <v>20.473684210526322</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A63" s="7">
-        <v>22</v>
-      </c>
-      <c r="B63" s="8">
-        <f t="shared" si="0"/>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="C63" s="8">
-        <f t="shared" si="1"/>
-        <v>20.947368421052641</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A64" s="7">
-        <v>23</v>
-      </c>
-      <c r="B64" s="8">
-        <f t="shared" si="0"/>
-        <v>25.888888888888889</v>
-      </c>
-      <c r="C64" s="8">
-        <f t="shared" si="1"/>
-        <v>21.421052631578956</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A65" s="7">
-        <v>24</v>
-      </c>
-      <c r="B65" s="8">
-        <f t="shared" si="0"/>
-        <v>27.111111111111114</v>
-      </c>
-      <c r="C65" s="8">
-        <f t="shared" si="1"/>
-        <v>21.894736842105271</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.45">
-      <c r="A66" s="7">
-        <v>25</v>
-      </c>
-      <c r="B66" s="8">
-        <f t="shared" si="0"/>
-        <v>28.333333333333336</v>
-      </c>
-      <c r="C66" s="8">
-        <f t="shared" si="1"/>
-        <v>22.368421052631586</v>
+    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A27" s="9">
+        <v>0</v>
+      </c>
+      <c r="B27" s="7">
+        <f t="shared" ref="B27" si="0">(A27*(1-$B$7*$B$10)-$B$8)/($B$7*$B$11)</f>
+        <v>-2.2222222222222223</v>
+      </c>
+      <c r="C27" s="7">
+        <f t="shared" ref="C27" si="1">($B$9+$B$7*$B$12*A27)/(1-$B$7*$B$13)</f>
+        <v>10.526315789473687</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A28" s="14">
+        <v>50</v>
+      </c>
+      <c r="B28" s="14">
+        <f t="shared" ref="B28" si="2">(A28*(1-$B$7*$B$10)-$B$8)/($B$7*$B$11)</f>
+        <v>58.888888888888893</v>
+      </c>
+      <c r="C28" s="14">
+        <f t="shared" ref="C28" si="3">($B$9+$B$7*$B$12*A28)/(1-$B$7*$B$13)</f>
+        <v>34.210526315789487</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="9"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" s="9">
+        <f>B22+B23</f>
+        <v>35.625000000000014</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="9">
+        <f>B59</f>
+        <v>35.625000000000014</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
